--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_7.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_7.xlsx
@@ -471,11 +471,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4893</v>
+        <v>81954</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vitor Gabriel Carvalho</t>
+          <t>Maria Cecília Rezende</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -485,147 +485,147 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45079</v>
+        <v>45102</v>
       </c>
       <c r="G2" t="n">
-        <v>4501.91</v>
+        <v>8834.209999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69247</v>
+        <v>88161</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sr. Henrique Costela</t>
+          <t>Dr. Pietro Pereira</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45094</v>
+        <v>45104</v>
       </c>
       <c r="G3" t="n">
-        <v>10579.33</v>
+        <v>11338.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55756</v>
+        <v>62554</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Joaquim da Luz</t>
+          <t>Emanuelly Ramos</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45085</v>
+        <v>45083</v>
       </c>
       <c r="G4" t="n">
-        <v>5858</v>
+        <v>7358.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>27763</v>
+        <v>68820</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Miguel Lima</t>
+          <t>Milena Lima</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45078</v>
+        <v>45084</v>
       </c>
       <c r="G5" t="n">
-        <v>10185.24</v>
+        <v>9348.709999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>38343</v>
+        <v>10245</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amanda Barros</t>
+          <t>Maria Costa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45084</v>
+        <v>45079</v>
       </c>
       <c r="G6" t="n">
-        <v>2781.45</v>
+        <v>11921.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89062</v>
+        <v>80176</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eduardo Aragão</t>
+          <t>Rebeca Pires</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -637,19 +637,19 @@
         <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45099</v>
+        <v>45106</v>
       </c>
       <c r="G7" t="n">
-        <v>7217.38</v>
+        <v>2842.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4740</v>
+        <v>67306</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lorena Barbosa</t>
+          <t>Sr. Pietro Teixeira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -659,104 +659,104 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45092</v>
+        <v>45094</v>
       </c>
       <c r="G8" t="n">
-        <v>12397.47</v>
+        <v>8005.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91801</v>
+        <v>79244</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gabriel Mendes</t>
+          <t>Beatriz Moura</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45083</v>
+        <v>45102</v>
       </c>
       <c r="G9" t="n">
-        <v>8984.17</v>
+        <v>8767.809999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>390</v>
+        <v>56927</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nina Pinto</t>
+          <t>Emilly da Costa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45104</v>
+        <v>45091</v>
       </c>
       <c r="G10" t="n">
-        <v>4717.34</v>
+        <v>10872.93</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>77145</v>
+        <v>32162</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sr. João Pedro Fogaça</t>
+          <t>Sra. Agatha Alves</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45083</v>
+        <v>45081</v>
       </c>
       <c r="G11" t="n">
-        <v>4261.4</v>
+        <v>6246.49</v>
       </c>
     </row>
   </sheetData>
